--- a/marketing_forms/006_marine_boat_show_lead_generation_form--marketing_forms.xlsx
+++ b/marketing_forms/006_marine_boat_show_lead_generation_form--marketing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1106,8 +1106,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Sales'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Marketing'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'product_development'}</t>
+          <t>product_development</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Product Development'}</t>
+          <t>Product Development</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'sail'}</t>
+          <t>sail</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Sail'}</t>
+          <t>Sail</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'motor'}</t>
+          <t>motor</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Motor'}</t>
+          <t>Motor</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'rowing'}</t>
+          <t>rowing</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Rowing'}</t>
+          <t>Rowing</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'france'}</t>
+          <t>france</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'France'}</t>
+          <t>France</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'italy'}</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Italy'}</t>
+          <t>Italy</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'spain'}</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Spain'}</t>
+          <t>Spain</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'mail'}</t>
+          <t>mail</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Mail'}</t>
+          <t>Mail</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'mail'}</t>
+          <t>mail</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Mail'}</t>
+          <t>Mail</t>
         </is>
       </c>
     </row>
